--- a/data/已处理/processed_equipment_log_field_profile.xlsx
+++ b/data/已处理/processed_equipment_log_field_profile.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,77 +429,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>field_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>line</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>base_name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>dtype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>missing_count</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>missing_ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unique_count</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>is_all_missing</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>is_numeric</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>is_onoff</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
@@ -512,7 +524,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>datetime64[ns]</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -588,7 +600,7 @@
         <v>20260422.99760674</v>
       </c>
       <c r="O3" t="n">
-        <v>2.002796995101813</v>
+        <v>2.002796995101764</v>
       </c>
     </row>
     <row r="4">
@@ -655,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -731,7 +743,7 @@
         <v>6.996075052651733</v>
       </c>
       <c r="O6" t="n">
-        <v>4.630355841661386</v>
+        <v>4.630355841661284</v>
       </c>
     </row>
     <row r="7">
@@ -919,7 +931,7 @@
         <v>4.122037143404174</v>
       </c>
       <c r="O10" t="n">
-        <v>3.187484306453274</v>
+        <v>3.187484306453764</v>
       </c>
     </row>
     <row r="11">
@@ -972,7 +984,7 @@
         <v>3.861650392494735</v>
       </c>
       <c r="O11" t="n">
-        <v>1.750337098004928</v>
+        <v>1.750337098004952</v>
       </c>
     </row>
     <row r="12">
@@ -1022,10 +1034,10 @@
         <v>6.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.564742485161785</v>
+        <v>2.564742485161784</v>
       </c>
       <c r="O12" t="n">
-        <v>2.558286822370231</v>
+        <v>2.558286822370396</v>
       </c>
     </row>
     <row r="13">
@@ -1078,7 +1090,7 @@
         <v>21.46084625694046</v>
       </c>
       <c r="O13" t="n">
-        <v>13.54073861756262</v>
+        <v>13.54073861756256</v>
       </c>
     </row>
     <row r="14">
@@ -1131,7 +1143,7 @@
         <v>60.7945625119663</v>
       </c>
       <c r="O14" t="n">
-        <v>38.35774902928547</v>
+        <v>38.35774902928421</v>
       </c>
     </row>
     <row r="15">
@@ -1184,7 +1196,7 @@
         <v>18.83017422937009</v>
       </c>
       <c r="O15" t="n">
-        <v>14.50608472084984</v>
+        <v>14.50608472084956</v>
       </c>
     </row>
     <row r="16">
@@ -1237,7 +1249,7 @@
         <v>54.65824238943136</v>
       </c>
       <c r="O16" t="n">
-        <v>42.15086075351667</v>
+        <v>42.15086075351994</v>
       </c>
     </row>
     <row r="17">
@@ -1312,7 +1324,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1388,7 +1400,7 @@
         <v>16.76591039632395</v>
       </c>
       <c r="O19" t="n">
-        <v>14.89433268290783</v>
+        <v>14.89433268290667</v>
       </c>
     </row>
     <row r="20">
@@ -1438,10 +1450,10 @@
         <v>20</v>
       </c>
       <c r="N20" t="n">
-        <v>6.796032931265557</v>
+        <v>6.796032931265555</v>
       </c>
       <c r="O20" t="n">
-        <v>6.041499130819663</v>
+        <v>6.041499130819916</v>
       </c>
     </row>
     <row r="21">
@@ -1463,7 +1475,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1536,10 +1548,10 @@
         <v>30</v>
       </c>
       <c r="N22" t="n">
-        <v>16.76817920735209</v>
+        <v>16.7681792073521</v>
       </c>
       <c r="O22" t="n">
-        <v>14.89455609028727</v>
+        <v>14.89455609028503</v>
       </c>
     </row>
     <row r="23">
@@ -1592,7 +1604,7 @@
         <v>6.799818112196055</v>
       </c>
       <c r="O23" t="n">
-        <v>6.043697053075627</v>
+        <v>6.043697053075621</v>
       </c>
     </row>
     <row r="24">
@@ -1614,7 +1626,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1690,7 +1702,7 @@
         <v>13.20776373731572</v>
       </c>
       <c r="O25" t="n">
-        <v>13.03698138799596</v>
+        <v>13.03698138799678</v>
       </c>
     </row>
     <row r="26">
@@ -1740,10 +1752,10 @@
         <v>7.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.572911162167337</v>
+        <v>2.572911162167336</v>
       </c>
       <c r="O26" t="n">
-        <v>2.438416890855662</v>
+        <v>2.438416890855643</v>
       </c>
     </row>
     <row r="27">
@@ -1765,7 +1777,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1841,7 +1853,7 @@
         <v>13.52788627225732</v>
       </c>
       <c r="O28" t="n">
-        <v>12.8277084859445</v>
+        <v>12.8277084859456</v>
       </c>
     </row>
     <row r="29">
@@ -1894,7 +1906,7 @@
         <v>2.430882634501244</v>
       </c>
       <c r="O29" t="n">
-        <v>2.207565065765734</v>
+        <v>2.207565065765768</v>
       </c>
     </row>
     <row r="30">
@@ -1916,7 +1928,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1989,10 +2001,10 @@
         <v>12.12</v>
       </c>
       <c r="N31" t="n">
-        <v>5.511777713957496</v>
+        <v>5.511777713957495</v>
       </c>
       <c r="O31" t="n">
-        <v>5.111696463604991</v>
+        <v>5.11169646360563</v>
       </c>
     </row>
     <row r="32">
@@ -2045,7 +2057,7 @@
         <v>2.022595251771013</v>
       </c>
       <c r="O32" t="n">
-        <v>1.843540808748419</v>
+        <v>1.843540808748359</v>
       </c>
     </row>
     <row r="33">
@@ -2067,7 +2079,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2140,10 +2152,10 @@
         <v>31.1</v>
       </c>
       <c r="N34" t="n">
-        <v>8.577685238368753</v>
+        <v>8.577685238368757</v>
       </c>
       <c r="O34" t="n">
-        <v>13.53423957325062</v>
+        <v>13.53423957325182</v>
       </c>
     </row>
     <row r="35">
@@ -2196,7 +2208,7 @@
         <v>50.57916905992725</v>
       </c>
       <c r="O35" t="n">
-        <v>7.909226678550749</v>
+        <v>7.909226678551778</v>
       </c>
     </row>
     <row r="36">
@@ -2302,7 +2314,7 @@
         <v>2.159630480566724</v>
       </c>
       <c r="O37" t="n">
-        <v>3.293836682839228</v>
+        <v>3.29383668283911</v>
       </c>
     </row>
     <row r="38">
@@ -2324,7 +2336,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2400,7 +2412,7 @@
         <v>17.36099942561746</v>
       </c>
       <c r="O39" t="n">
-        <v>17.06523880321686</v>
+        <v>17.06523880321853</v>
       </c>
     </row>
     <row r="40">
@@ -2453,7 +2465,7 @@
         <v>31.38809113536282</v>
       </c>
       <c r="O40" t="n">
-        <v>25.29722345357773</v>
+        <v>25.29722345357926</v>
       </c>
     </row>
     <row r="41">
@@ -2506,7 +2518,7 @@
         <v>6.282787669921501</v>
       </c>
       <c r="O41" t="n">
-        <v>4.834856735989646</v>
+        <v>4.834856735990262</v>
       </c>
     </row>
     <row r="42">
@@ -2559,7 +2571,7 @@
         <v>4.009228412789585</v>
       </c>
       <c r="O42" t="n">
-        <v>3.918452747821299</v>
+        <v>3.918452747821237</v>
       </c>
     </row>
     <row r="43">
@@ -2581,7 +2593,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2657,7 +2669,7 @@
         <v>5.714208309400727</v>
       </c>
       <c r="O44" t="n">
-        <v>5.506511843786023</v>
+        <v>5.506511843786041</v>
       </c>
     </row>
     <row r="45">
@@ -2710,7 +2722,7 @@
         <v>6.773782309017807</v>
       </c>
       <c r="O45" t="n">
-        <v>6.212871078102546</v>
+        <v>6.212871078102488</v>
       </c>
     </row>
     <row r="46">
@@ -2732,7 +2744,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2805,10 +2817,10 @@
         <v>13.32</v>
       </c>
       <c r="N47" t="n">
-        <v>5.71682557916906</v>
+        <v>5.716825579169059</v>
       </c>
       <c r="O47" t="n">
-        <v>5.506746698301434</v>
+        <v>5.506746698301681</v>
       </c>
     </row>
     <row r="48">
@@ -2861,7 +2873,7 @@
         <v>6.107643116982577</v>
       </c>
       <c r="O48" t="n">
-        <v>5.558034058190863</v>
+        <v>5.558034058190836</v>
       </c>
     </row>
     <row r="49">
@@ -2883,7 +2895,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2959,7 +2971,7 @@
         <v>0.03455964005360904</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3677446462932958</v>
+        <v>0.3677446462933617</v>
       </c>
     </row>
     <row r="51">
@@ -3012,7 +3024,7 @@
         <v>0.04899674516561363</v>
       </c>
       <c r="O51" t="n">
-        <v>0.513672561855499</v>
+        <v>0.5136725618554435</v>
       </c>
     </row>
     <row r="52">
@@ -3065,7 +3077,7 @@
         <v>28.8456059735784</v>
       </c>
       <c r="O52" t="n">
-        <v>98.58877164770719</v>
+        <v>98.58877164770738</v>
       </c>
     </row>
     <row r="53">
@@ -3118,7 +3130,7 @@
         <v>27.78780394409344</v>
       </c>
       <c r="O53" t="n">
-        <v>138.6909629432559</v>
+        <v>138.6909629432372</v>
       </c>
     </row>
     <row r="54">
@@ -3171,7 +3183,7 @@
         <v>22.11576680068926</v>
       </c>
       <c r="O54" t="n">
-        <v>138.6906807333476</v>
+        <v>138.6906807333428</v>
       </c>
     </row>
     <row r="55">
@@ -3221,10 +3233,10 @@
         <v>29.8</v>
       </c>
       <c r="N55" t="n">
-        <v>20.42419107792457</v>
+        <v>20.42419107792456</v>
       </c>
       <c r="O55" t="n">
-        <v>169.8328257900596</v>
+        <v>169.8328257900605</v>
       </c>
     </row>
     <row r="56">
@@ -3277,7 +3289,7 @@
         <v>140.9290446103772</v>
       </c>
       <c r="O56" t="n">
-        <v>172.5613973495487</v>
+        <v>172.5613973495553</v>
       </c>
     </row>
     <row r="57">
@@ -3330,7 +3342,7 @@
         <v>141.0138521922267</v>
       </c>
       <c r="O57" t="n">
-        <v>172.4864490402004</v>
+        <v>172.4864490401842</v>
       </c>
     </row>
     <row r="58">
@@ -3383,7 +3395,7 @@
         <v>1026.215805857266</v>
       </c>
       <c r="O58" t="n">
-        <v>900.0091612864962</v>
+        <v>900.0091612864838</v>
       </c>
     </row>
     <row r="59">
@@ -3436,7 +3448,7 @@
         <v>7.395211826536474</v>
       </c>
       <c r="O59" t="n">
-        <v>6.46836162614502</v>
+        <v>6.468361626144953</v>
       </c>
     </row>
     <row r="60">
@@ -3486,10 +3498,10 @@
         <v>12.480941</v>
       </c>
       <c r="N60" t="n">
-        <v>6.524918189450507</v>
+        <v>6.524918189450508</v>
       </c>
       <c r="O60" t="n">
-        <v>5.660737165572483</v>
+        <v>5.660737165572569</v>
       </c>
     </row>
     <row r="61">
@@ -3542,7 +3554,7 @@
         <v>1.528914712808731</v>
       </c>
       <c r="O61" t="n">
-        <v>2.221630646599877</v>
+        <v>2.221630646599664</v>
       </c>
     </row>
     <row r="62">
@@ -3592,10 +3604,10 @@
         <v>4.952311</v>
       </c>
       <c r="N62" t="n">
-        <v>2.380593188397473</v>
+        <v>2.380593188397472</v>
       </c>
       <c r="O62" t="n">
-        <v>2.295387274946031</v>
+        <v>2.295387274946022</v>
       </c>
     </row>
     <row r="63">
@@ -3648,7 +3660,7 @@
         <v>0.7488464646754739</v>
       </c>
       <c r="O63" t="n">
-        <v>5.471449679366035</v>
+        <v>5.471449679366199</v>
       </c>
     </row>
     <row r="64">
@@ -3701,7 +3713,7 @@
         <v>1581.261505343959</v>
       </c>
       <c r="O64" t="n">
-        <v>1372.873213896115</v>
+        <v>1372.873213896069</v>
       </c>
     </row>
     <row r="65">
@@ -3754,7 +3766,7 @@
         <v>51.96735601368945</v>
       </c>
       <c r="O65" t="n">
-        <v>5.864772235702219</v>
+        <v>5.864772235702213</v>
       </c>
     </row>
     <row r="66">
@@ -3807,7 +3819,7 @@
         <v>18.70567043490331</v>
       </c>
       <c r="O66" t="n">
-        <v>2.943089393627005</v>
+        <v>2.943089393627028</v>
       </c>
     </row>
     <row r="67">
@@ -3860,7 +3872,7 @@
         <v>8.009624165230711</v>
       </c>
       <c r="O67" t="n">
-        <v>0.03474682013131548</v>
+        <v>0.0347468201313154</v>
       </c>
     </row>
     <row r="68">
@@ -3910,10 +3922,10 @@
         <v>2.08904</v>
       </c>
       <c r="N68" t="n">
-        <v>0.8976965196247367</v>
+        <v>0.8976965196247368</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1517620562058874</v>
+        <v>0.1517620562058879</v>
       </c>
     </row>
     <row r="69">
@@ -3966,7 +3978,7 @@
         <v>1.063065312081179</v>
       </c>
       <c r="O69" t="n">
-        <v>0.1604273682286061</v>
+        <v>0.1604273682286062</v>
       </c>
     </row>
     <row r="70">
@@ -4019,7 +4031,7 @@
         <v>0.9471617243921119</v>
       </c>
       <c r="O70" t="n">
-        <v>0.150273144827013</v>
+        <v>0.1502731448270132</v>
       </c>
     </row>
     <row r="71">
@@ -4072,7 +4084,7 @@
         <v>0.9633874314570171</v>
       </c>
       <c r="O71" t="n">
-        <v>0.1500171397281046</v>
+        <v>0.1500171397281055</v>
       </c>
     </row>
     <row r="72">
@@ -4094,7 +4106,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -4170,7 +4182,7 @@
         <v>3.798295998468313</v>
       </c>
       <c r="O73" t="n">
-        <v>1.32682345310454</v>
+        <v>1.326823453104469</v>
       </c>
     </row>
     <row r="74">
@@ -4358,7 +4370,7 @@
         <v>3.907907332950411</v>
       </c>
       <c r="O77" t="n">
-        <v>2.60860612808431</v>
+        <v>2.608606128084295</v>
       </c>
     </row>
     <row r="78">
@@ -4411,7 +4423,7 @@
         <v>3.646075052651733</v>
       </c>
       <c r="O78" t="n">
-        <v>1.260880043908892</v>
+        <v>1.260880043908868</v>
       </c>
     </row>
     <row r="79">
@@ -4464,7 +4476,7 @@
         <v>1.524995213478844</v>
       </c>
       <c r="O79" t="n">
-        <v>1.677964749710068</v>
+        <v>1.677964749710157</v>
       </c>
     </row>
     <row r="80">
@@ -4517,7 +4529,7 @@
         <v>4.745357074478269</v>
       </c>
       <c r="O80" t="n">
-        <v>10.94952364067469</v>
+        <v>10.94952364067505</v>
       </c>
     </row>
     <row r="81">
@@ -4570,7 +4582,7 @@
         <v>13.43767949454337</v>
       </c>
       <c r="O81" t="n">
-        <v>31.00572520728355</v>
+        <v>31.00572520728344</v>
       </c>
     </row>
     <row r="82">
@@ -4623,7 +4635,7 @@
         <v>35.48726785372391</v>
       </c>
       <c r="O82" t="n">
-        <v>5.001386180512353</v>
+        <v>5.001386180512223</v>
       </c>
     </row>
     <row r="83">
@@ -4676,7 +4688,7 @@
         <v>78.28307486119088</v>
       </c>
       <c r="O83" t="n">
-        <v>6.913830206340902</v>
+        <v>6.913830206341742</v>
       </c>
     </row>
     <row r="84">
@@ -4729,7 +4741,7 @@
         <v>159232.2333037327</v>
       </c>
       <c r="O84" t="n">
-        <v>241762.150424592</v>
+        <v>241762.1504245953</v>
       </c>
     </row>
     <row r="85">
@@ -4751,7 +4763,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -4827,7 +4839,7 @@
         <v>14.36659965537048</v>
       </c>
       <c r="O86" t="n">
-        <v>16.18665140588799</v>
+        <v>16.18665140588607</v>
       </c>
     </row>
     <row r="87">
@@ -4877,10 +4889,10 @@
         <v>16.51</v>
       </c>
       <c r="N87" t="n">
-        <v>6.610894122152019</v>
+        <v>6.610894122152021</v>
       </c>
       <c r="O87" t="n">
-        <v>7.336374013878233</v>
+        <v>7.336374013878193</v>
       </c>
     </row>
     <row r="88">
@@ -4902,7 +4914,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -4978,7 +4990,7 @@
         <v>14.37475588742102</v>
       </c>
       <c r="O89" t="n">
-        <v>16.18634637032861</v>
+        <v>16.18634637033087</v>
       </c>
     </row>
     <row r="90">
@@ -5031,7 +5043,7 @@
         <v>5.934908098793797</v>
       </c>
       <c r="O90" t="n">
-        <v>6.587277639367535</v>
+        <v>6.587277639367392</v>
       </c>
     </row>
     <row r="91">
@@ -5053,7 +5065,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5129,7 +5141,7 @@
         <v>9.346084625694045</v>
       </c>
       <c r="O92" t="n">
-        <v>17.84624157704235</v>
+        <v>17.84624157704722</v>
       </c>
     </row>
     <row r="93">
@@ -5182,7 +5194,7 @@
         <v>1.670397281255983</v>
       </c>
       <c r="O93" t="n">
-        <v>2.248665870117562</v>
+        <v>2.248665870117308</v>
       </c>
     </row>
     <row r="94">
@@ -5204,7 +5216,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -5280,7 +5292,7 @@
         <v>8.241240666283746</v>
       </c>
       <c r="O95" t="n">
-        <v>16.49937583431763</v>
+        <v>16.49937583431678</v>
       </c>
     </row>
     <row r="96">
@@ -5333,7 +5345,7 @@
         <v>1.550269959793222</v>
       </c>
       <c r="O96" t="n">
-        <v>2.133644823648354</v>
+        <v>2.133644823648276</v>
       </c>
     </row>
     <row r="97">
@@ -5355,7 +5367,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5431,7 +5443,7 @@
         <v>3.646741336396707</v>
       </c>
       <c r="O98" t="n">
-        <v>4.446820541919091</v>
+        <v>4.446820541918636</v>
       </c>
     </row>
     <row r="99">
@@ -5484,7 +5496,7 @@
         <v>2.044784606547961</v>
       </c>
       <c r="O99" t="n">
-        <v>2.320020754462323</v>
+        <v>2.320020754462295</v>
       </c>
     </row>
     <row r="100">
@@ -5506,7 +5518,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -5582,7 +5594,7 @@
         <v>0.1091805475780203</v>
       </c>
       <c r="O101" t="n">
-        <v>1.172603718916489</v>
+        <v>1.172603718916486</v>
       </c>
     </row>
     <row r="102">
@@ -5635,7 +5647,7 @@
         <v>52.25923798583189</v>
       </c>
       <c r="O102" t="n">
-        <v>9.753702067643495</v>
+        <v>9.753702067642347</v>
       </c>
     </row>
     <row r="103">
@@ -5688,7 +5700,7 @@
         <v>9.999042695768715</v>
       </c>
       <c r="O103" t="n">
-        <v>0.09784192512847968</v>
+        <v>0.09784192512847542</v>
       </c>
     </row>
     <row r="104">
@@ -5741,7 +5753,7 @@
         <v>0.08010721807390388</v>
       </c>
       <c r="O104" t="n">
-        <v>0.8604877038930039</v>
+        <v>0.8604877038929747</v>
       </c>
     </row>
     <row r="105">
@@ -5763,7 +5775,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -5839,7 +5851,7 @@
         <v>5.595988895270917</v>
       </c>
       <c r="O106" t="n">
-        <v>7.857680347515124</v>
+        <v>7.857680347515199</v>
       </c>
     </row>
     <row r="107">
@@ -5892,7 +5904,7 @@
         <v>51.86578594677388</v>
       </c>
       <c r="O107" t="n">
-        <v>9.696869609309488</v>
+        <v>9.696869609308953</v>
       </c>
     </row>
     <row r="108">
@@ -5945,7 +5957,7 @@
         <v>9.998085391537431</v>
       </c>
       <c r="O108" t="n">
-        <v>0.1383627536132251</v>
+        <v>0.1383627536132131</v>
       </c>
     </row>
     <row r="109">
@@ -5998,7 +6010,7 @@
         <v>2.212406662837449</v>
       </c>
       <c r="O109" t="n">
-        <v>2.604920999335849</v>
+        <v>2.60492099933584</v>
       </c>
     </row>
     <row r="110">
@@ -6020,7 +6032,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6093,10 +6105,10 @@
         <v>11.12</v>
       </c>
       <c r="N111" t="n">
-        <v>2.693061458931648</v>
+        <v>2.693061458931649</v>
       </c>
       <c r="O111" t="n">
-        <v>3.557442539814615</v>
+        <v>3.55744253981464</v>
       </c>
     </row>
     <row r="112">
@@ -6149,7 +6161,7 @@
         <v>4.000257514838216</v>
       </c>
       <c r="O112" t="n">
-        <v>4.727433791647153</v>
+        <v>4.727433791647074</v>
       </c>
     </row>
     <row r="113">
@@ -6171,7 +6183,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6247,7 +6259,7 @@
         <v>2.697752249664944</v>
       </c>
       <c r="O114" t="n">
-        <v>3.557736244110024</v>
+        <v>3.557736244109731</v>
       </c>
     </row>
     <row r="115">
@@ -6297,10 +6309,10 @@
         <v>20</v>
       </c>
       <c r="N115" t="n">
-        <v>3.678518093049972</v>
+        <v>3.678518093049971</v>
       </c>
       <c r="O115" t="n">
-        <v>4.268833767979098</v>
+        <v>4.268833767978814</v>
       </c>
     </row>
     <row r="116">
@@ -6322,7 +6334,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6395,10 +6407,10 @@
         <v>3.15</v>
       </c>
       <c r="N117" t="n">
-        <v>0.7900670112961898</v>
+        <v>0.7900670112961896</v>
       </c>
       <c r="O117" t="n">
-        <v>1.241906992410153</v>
+        <v>1.241906992410263</v>
       </c>
     </row>
     <row r="118">
@@ -6451,7 +6463,7 @@
         <v>1.501928968026039</v>
       </c>
       <c r="O118" t="n">
-        <v>2.403531027632905</v>
+        <v>2.403531027632638</v>
       </c>
     </row>
     <row r="119">
@@ -6501,10 +6513,10 @@
         <v>30.7</v>
       </c>
       <c r="N119" t="n">
-        <v>28.96569978939306</v>
+        <v>28.96569978939307</v>
       </c>
       <c r="O119" t="n">
-        <v>98.0765493667342</v>
+        <v>98.07654936672779</v>
       </c>
     </row>
     <row r="120">
@@ -6557,7 +6569,7 @@
         <v>27.66588167719701</v>
       </c>
       <c r="O120" t="n">
-        <v>138.6896941202482</v>
+        <v>138.6896941202265</v>
       </c>
     </row>
     <row r="121">
@@ -6610,7 +6622,7 @@
         <v>30.99311698257706</v>
       </c>
       <c r="O121" t="n">
-        <v>169.9322330098441</v>
+        <v>169.9322330098515</v>
       </c>
     </row>
     <row r="122">
@@ -6663,7 +6675,7 @@
         <v>21.63477886272257</v>
       </c>
       <c r="O122" t="n">
-        <v>169.8502588101882</v>
+        <v>169.850258810186</v>
       </c>
     </row>
     <row r="123">
@@ -6716,7 +6728,7 @@
         <v>139.7973769864063</v>
       </c>
       <c r="O123" t="n">
-        <v>172.9294285034238</v>
+        <v>172.9294285034246</v>
       </c>
     </row>
     <row r="124">
@@ -6769,7 +6781,7 @@
         <v>140.0816197587593</v>
       </c>
       <c r="O124" t="n">
-        <v>172.6790182957886</v>
+        <v>172.6790182958119</v>
       </c>
     </row>
     <row r="125">
@@ -6822,7 +6834,7 @@
         <v>880.4803507320505</v>
       </c>
       <c r="O125" t="n">
-        <v>931.0329478040447</v>
+        <v>931.0329478040798</v>
       </c>
     </row>
     <row r="126">
@@ -6872,10 +6884,10 @@
         <v>19.828794</v>
       </c>
       <c r="N126" t="n">
-        <v>5.811374502584721</v>
+        <v>5.811374502584722</v>
       </c>
       <c r="O126" t="n">
-        <v>6.277980806082042</v>
+        <v>6.277980806081931</v>
       </c>
     </row>
     <row r="127">
@@ -6928,7 +6940,7 @@
         <v>3.924269884357649</v>
       </c>
       <c r="O127" t="n">
-        <v>4.118891605858722</v>
+        <v>4.118891605858471</v>
       </c>
     </row>
     <row r="128">
@@ -6981,7 +6993,7 @@
         <v>1.552053575722765</v>
       </c>
       <c r="O128" t="n">
-        <v>1.68905616442714</v>
+        <v>1.689056164427159</v>
       </c>
     </row>
     <row r="129">
@@ -7031,10 +7043,10 @@
         <v>3.580415</v>
       </c>
       <c r="N129" t="n">
-        <v>0.03745133323760291</v>
+        <v>0.03745133323760292</v>
       </c>
       <c r="O129" t="n">
-        <v>0.3193295751288796</v>
+        <v>0.3193295751288816</v>
       </c>
     </row>
     <row r="130">
@@ -7087,7 +7099,7 @@
         <v>18.14932526163124</v>
       </c>
       <c r="O130" t="n">
-        <v>15.77500147026843</v>
+        <v>15.77500147026844</v>
       </c>
     </row>
     <row r="131">
@@ -7140,7 +7152,7 @@
         <v>1552.986552292265</v>
       </c>
       <c r="O131" t="n">
-        <v>1628.305360101927</v>
+        <v>1628.305360101993</v>
       </c>
     </row>
     <row r="132">
@@ -7190,10 +7202,10 @@
         <v>91.99858999999999</v>
       </c>
       <c r="N132" t="n">
-        <v>50.42158718629141</v>
+        <v>50.4215871862914</v>
       </c>
       <c r="O132" t="n">
-        <v>7.727679486328464</v>
+        <v>7.727679486328424</v>
       </c>
     </row>
     <row r="133">
@@ -7246,7 +7258,7 @@
         <v>26.80008394667816</v>
       </c>
       <c r="O133" t="n">
-        <v>9.288115678231073</v>
+        <v>9.288115678231032</v>
       </c>
     </row>
     <row r="134">
@@ -7349,10 +7361,10 @@
         <v>1.760739</v>
       </c>
       <c r="N135" t="n">
-        <v>0.9517339841087498</v>
+        <v>0.9517339841087499</v>
       </c>
       <c r="O135" t="n">
-        <v>0.1519500111386323</v>
+        <v>0.151950011138632</v>
       </c>
     </row>
     <row r="136">
@@ -7402,10 +7414,10 @@
         <v>1.525303</v>
       </c>
       <c r="N136" t="n">
-        <v>1.091560373827303</v>
+        <v>1.091560373827302</v>
       </c>
       <c r="O136" t="n">
-        <v>0.1601623528401473</v>
+        <v>0.1601623528401468</v>
       </c>
     </row>
     <row r="137">
@@ -7458,7 +7470,7 @@
         <v>5.736380910204863</v>
       </c>
       <c r="O137" t="n">
-        <v>0.1263123809405303</v>
+        <v>0.1263123809405302</v>
       </c>
     </row>
     <row r="138">
@@ -7511,7 +7523,7 @@
         <v>5.743338028049014</v>
       </c>
       <c r="O138" t="n">
-        <v>0.1268796207831294</v>
+        <v>0.1268796207831289</v>
       </c>
     </row>
     <row r="139">
@@ -7533,7 +7545,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7606,10 +7618,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="N140" t="n">
-        <v>68.65313038483632</v>
+        <v>68.6531303848363</v>
       </c>
       <c r="O140" t="n">
-        <v>38.26987020238584</v>
+        <v>38.26987020239017</v>
       </c>
     </row>
     <row r="141">
@@ -7662,7 +7674,7 @@
         <v>3.744891824621865</v>
       </c>
       <c r="O141" t="n">
-        <v>2.138022946205865</v>
+        <v>2.138022946205909</v>
       </c>
     </row>
     <row r="142">
@@ -7684,7 +7696,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -7760,7 +7772,7 @@
         <v>30.61601569978939</v>
       </c>
       <c r="O143" t="n">
-        <v>16.94781377139292</v>
+        <v>16.94781377138981</v>
       </c>
     </row>
     <row r="144">
@@ -7813,7 +7825,7 @@
         <v>4.24482098410875</v>
       </c>
       <c r="O144" t="n">
-        <v>2.350831131663218</v>
+        <v>2.350831131663233</v>
       </c>
     </row>
     <row r="145">
@@ -7866,7 +7878,7 @@
         <v>59.20992724487842</v>
       </c>
       <c r="O145" t="n">
-        <v>98.42195676784209</v>
+        <v>98.4219567678356</v>
       </c>
     </row>
     <row r="146">
@@ -7916,10 +7928,10 @@
         <v>61.5</v>
       </c>
       <c r="N146" t="n">
-        <v>59.16812176909821</v>
+        <v>59.16812176909823</v>
       </c>
       <c r="O146" t="n">
-        <v>98.42110151785269</v>
+        <v>98.42110151784166</v>
       </c>
     </row>
     <row r="147">
@@ -7972,7 +7984,7 @@
         <v>59.04909056098028</v>
       </c>
       <c r="O147" t="n">
-        <v>139.2002606309633</v>
+        <v>139.2002606309573</v>
       </c>
     </row>
     <row r="148">
@@ -8025,7 +8037,7 @@
         <v>25.98268236645606</v>
       </c>
       <c r="O148" t="n">
-        <v>138.7351013765883</v>
+        <v>138.7351013765672</v>
       </c>
     </row>
     <row r="149">
@@ -8078,7 +8090,7 @@
         <v>63.8499329887038</v>
       </c>
       <c r="O149" t="n">
-        <v>139.2659461749261</v>
+        <v>139.2659461749126</v>
       </c>
     </row>
     <row r="150">
@@ -8128,10 +8140,10 @@
         <v>45.7</v>
       </c>
       <c r="N150" t="n">
-        <v>43.10179973195482</v>
+        <v>43.10179973195481</v>
       </c>
       <c r="O150" t="n">
-        <v>138.9719516787133</v>
+        <v>138.9719516787141</v>
       </c>
     </row>
     <row r="151">
@@ -8184,7 +8196,7 @@
         <v>40.81888761248324</v>
       </c>
       <c r="O151" t="n">
-        <v>138.9719013251239</v>
+        <v>138.971901325124</v>
       </c>
     </row>
     <row r="152">
@@ -8237,7 +8249,7 @@
         <v>10.43686578594677</v>
       </c>
       <c r="O152" t="n">
-        <v>138.5209014590327</v>
+        <v>138.520901459037</v>
       </c>
     </row>
     <row r="153">
@@ -8287,10 +8299,10 @@
         <v>12.4</v>
       </c>
       <c r="N153" t="n">
-        <v>9.98426191843768</v>
+        <v>9.984261918437682</v>
       </c>
       <c r="O153" t="n">
-        <v>138.5136360894994</v>
+        <v>138.513636089517</v>
       </c>
     </row>
     <row r="154">
@@ -8343,7 +8355,7 @@
         <v>43.03801455102431</v>
       </c>
       <c r="O154" t="n">
-        <v>138.9713956862952</v>
+        <v>138.9713956862927</v>
       </c>
     </row>
     <row r="155">
@@ -8396,7 +8408,7 @@
         <v>40.77588550641394</v>
       </c>
       <c r="O155" t="n">
-        <v>170.1851704492451</v>
+        <v>170.1851704492484</v>
       </c>
     </row>
     <row r="156">
@@ -8552,10 +8564,10 @@
         <v>253827.408</v>
       </c>
       <c r="N158" t="n">
-        <v>92143.81013805915</v>
+        <v>92143.81013805917</v>
       </c>
       <c r="O158" t="n">
-        <v>83769.67245294082</v>
+        <v>83769.67245294117</v>
       </c>
     </row>
     <row r="159">
@@ -8608,7 +8620,7 @@
         <v>0.7326249282021826</v>
       </c>
       <c r="O159" t="n">
-        <v>7.208992718126561</v>
+        <v>7.208992718126024</v>
       </c>
     </row>
     <row r="160">
@@ -8661,7 +8673,7 @@
         <v>1.704862706490523</v>
       </c>
       <c r="O160" t="n">
-        <v>5.480014121319509</v>
+        <v>5.480014121319283</v>
       </c>
     </row>
     <row r="161">
@@ -8714,7 +8726,7 @@
         <v>0.0880153092092667</v>
       </c>
       <c r="O161" t="n">
-        <v>1.548644828543725</v>
+        <v>1.548644828543889</v>
       </c>
     </row>
     <row r="162">
@@ -8767,7 +8779,7 @@
         <v>26.56044859640054</v>
       </c>
       <c r="O162" t="n">
-        <v>11.04330070719108</v>
+        <v>11.04330070719121</v>
       </c>
     </row>
     <row r="163">
@@ -8817,10 +8829,10 @@
         <v>18.740808</v>
       </c>
       <c r="N163" t="n">
-        <v>7.87527416542217</v>
+        <v>7.875274165422172</v>
       </c>
       <c r="O163" t="n">
-        <v>7.427809116150158</v>
+        <v>7.427809116150036</v>
       </c>
     </row>
     <row r="164">
@@ -8873,7 +8885,7 @@
         <v>16.96207810118706</v>
       </c>
       <c r="O164" t="n">
-        <v>17.77307663661252</v>
+        <v>17.77307663661151</v>
       </c>
     </row>
     <row r="165">
@@ -8926,7 +8938,7 @@
         <v>1.702885578977599</v>
       </c>
       <c r="O165" t="n">
-        <v>1.699617752407818</v>
+        <v>1.699617752407825</v>
       </c>
     </row>
     <row r="166">
@@ -8976,10 +8988,10 @@
         <v>2.250222</v>
       </c>
       <c r="N166" t="n">
-        <v>0.2989835646180355</v>
+        <v>0.2989835646180357</v>
       </c>
       <c r="O166" t="n">
-        <v>0.4501459576942666</v>
+        <v>0.4501459576942841</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9041,10 @@
         <v>1.474398</v>
       </c>
       <c r="N167" t="n">
-        <v>0.9147562254451465</v>
+        <v>0.9147562254451466</v>
       </c>
       <c r="O167" t="n">
-        <v>0.1171290592852123</v>
+        <v>0.1171290592852135</v>
       </c>
     </row>
     <row r="168">
@@ -9244,7 +9256,7 @@
         <v>7.519002165900823</v>
       </c>
       <c r="O171" t="n">
-        <v>0.4113774091520608</v>
+        <v>0.4113774091520602</v>
       </c>
     </row>
     <row r="172">
@@ -9297,7 +9309,7 @@
         <v>8.24776483697109</v>
       </c>
       <c r="O172" t="n">
-        <v>0.3992419265633376</v>
+        <v>0.3992419265633381</v>
       </c>
     </row>
     <row r="173">
@@ -9347,10 +9359,10 @@
         <v>5.138357</v>
       </c>
       <c r="N173" t="n">
-        <v>4.895374714148956</v>
+        <v>4.895374714148957</v>
       </c>
       <c r="O173" t="n">
-        <v>0.0220521859862092</v>
+        <v>0.02205218598621059</v>
       </c>
     </row>
     <row r="174">
@@ -9403,7 +9415,7 @@
         <v>5.977998818112196</v>
       </c>
       <c r="O174" t="n">
-        <v>0.03483415066269077</v>
+        <v>0.03483415066269094</v>
       </c>
     </row>
     <row r="175">
@@ -9456,7 +9468,7 @@
         <v>1.087763251771013</v>
       </c>
       <c r="O175" t="n">
-        <v>0.04335524171084315</v>
+        <v>0.04335524171084323</v>
       </c>
     </row>
     <row r="176">
@@ -9509,7 +9521,7 @@
         <v>0.9196565073743016</v>
       </c>
       <c r="O176" t="n">
-        <v>0.1516553409982322</v>
+        <v>0.1516553409982321</v>
       </c>
     </row>
     <row r="177">
@@ -9531,7 +9543,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>datetime64[ns]</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -9576,7 +9588,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -9652,7 +9664,7 @@
         <v>20260422.99760674</v>
       </c>
       <c r="O179" t="n">
-        <v>2.002749060082836</v>
+        <v>2.002749060083229</v>
       </c>
     </row>
     <row r="180">
@@ -9719,7 +9731,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -9795,7 +9807,7 @@
         <v>5.397185525560023</v>
       </c>
       <c r="O182" t="n">
-        <v>3.762491549484811</v>
+        <v>3.762491549485534</v>
       </c>
     </row>
     <row r="183">
@@ -9983,7 +9995,7 @@
         <v>4.014972238177293</v>
       </c>
       <c r="O186" t="n">
-        <v>2.914360732140524</v>
+        <v>2.914360732140149</v>
       </c>
     </row>
     <row r="187">
@@ -10036,7 +10048,7 @@
         <v>3.753862722573234</v>
       </c>
       <c r="O187" t="n">
-        <v>1.529135894266995</v>
+        <v>1.529135894267104</v>
       </c>
     </row>
     <row r="188">
@@ -10089,7 +10101,7 @@
         <v>2.044868849320314</v>
       </c>
       <c r="O188" t="n">
-        <v>2.224917096949603</v>
+        <v>2.22491709694959</v>
       </c>
     </row>
     <row r="189">
@@ -10142,7 +10154,7 @@
         <v>13.10310166570936</v>
       </c>
       <c r="O189" t="n">
-        <v>14.88186196894812</v>
+        <v>14.881861968947</v>
       </c>
     </row>
     <row r="190">
@@ -10195,7 +10207,7 @@
         <v>37.11612100325483</v>
       </c>
       <c r="O190" t="n">
-        <v>42.15415946539423</v>
+        <v>42.15415946539071</v>
       </c>
     </row>
     <row r="191">
@@ -10248,7 +10260,7 @@
         <v>27.158721041547</v>
       </c>
       <c r="O191" t="n">
-        <v>13.67781255076154</v>
+        <v>13.67781255076347</v>
       </c>
     </row>
     <row r="192">
@@ -10301,7 +10313,7 @@
         <v>66.47065862531112</v>
       </c>
       <c r="O192" t="n">
-        <v>32.43060660225714</v>
+        <v>32.43060660225008</v>
       </c>
     </row>
     <row r="193">
@@ -10354,7 +10366,7 @@
         <v>183705.1720537003</v>
       </c>
       <c r="O193" t="n">
-        <v>254250.3877001847</v>
+        <v>254250.3877001779</v>
       </c>
     </row>
     <row r="194">
@@ -10376,7 +10388,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -10452,7 +10464,7 @@
         <v>15.56625502584721</v>
       </c>
       <c r="O195" t="n">
-        <v>15.59974603903446</v>
+        <v>15.59974603903544</v>
       </c>
     </row>
     <row r="196">
@@ -10505,7 +10517,7 @@
         <v>6.703463526708787</v>
       </c>
       <c r="O196" t="n">
-        <v>6.720673736156733</v>
+        <v>6.720673736157383</v>
       </c>
     </row>
     <row r="197">
@@ -10527,7 +10539,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -10603,7 +10615,7 @@
         <v>15.57146754738656</v>
       </c>
       <c r="O198" t="n">
-        <v>15.5994683269013</v>
+        <v>15.59946832690212</v>
       </c>
     </row>
     <row r="199">
@@ -10656,7 +10668,7 @@
         <v>6.367363105494927</v>
       </c>
       <c r="O199" t="n">
-        <v>6.335958011151834</v>
+        <v>6.335958011152137</v>
       </c>
     </row>
     <row r="200">
@@ -10678,7 +10690,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -10754,7 +10766,7 @@
         <v>11.27692418150488</v>
       </c>
       <c r="O201" t="n">
-        <v>15.7461817735458</v>
+        <v>15.74618177354419</v>
       </c>
     </row>
     <row r="202">
@@ -10807,7 +10819,7 @@
         <v>2.12165422171166</v>
       </c>
       <c r="O202" t="n">
-        <v>2.388423498903469</v>
+        <v>2.388423498903236</v>
       </c>
     </row>
     <row r="203">
@@ -10829,7 +10841,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -10905,7 +10917,7 @@
         <v>10.88456346927053</v>
       </c>
       <c r="O204" t="n">
-        <v>15.01222135753207</v>
+        <v>15.01222135753433</v>
       </c>
     </row>
     <row r="205">
@@ -10955,10 +10967,10 @@
         <v>7.17</v>
       </c>
       <c r="N205" t="n">
-        <v>1.990576297147233</v>
+        <v>1.990576297147234</v>
       </c>
       <c r="O205" t="n">
-        <v>2.215072286166203</v>
+        <v>2.215072286166099</v>
       </c>
     </row>
     <row r="206">
@@ -10980,7 +10992,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -11053,10 +11065,10 @@
         <v>13.02</v>
       </c>
       <c r="N207" t="n">
-        <v>4.579259525177102</v>
+        <v>4.579259525177101</v>
       </c>
       <c r="O207" t="n">
-        <v>4.880610615990049</v>
+        <v>4.880610615989984</v>
       </c>
     </row>
     <row r="208">
@@ -11109,7 +11121,7 @@
         <v>2.033689929159487</v>
       </c>
       <c r="O208" t="n">
-        <v>2.095347808715495</v>
+        <v>2.095347808715577</v>
       </c>
     </row>
     <row r="209">
@@ -11131,7 +11143,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -11204,10 +11216,10 @@
         <v>31.1</v>
       </c>
       <c r="N210" t="n">
-        <v>4.343432892973387</v>
+        <v>4.343432892973389</v>
       </c>
       <c r="O210" t="n">
-        <v>10.49764994179917</v>
+        <v>10.49764994179632</v>
       </c>
     </row>
     <row r="211">
@@ -11260,7 +11272,7 @@
         <v>51.41920352287957</v>
       </c>
       <c r="O211" t="n">
-        <v>8.918923863821355</v>
+        <v>8.918923863822172</v>
       </c>
     </row>
     <row r="212">
@@ -11313,7 +11325,7 @@
         <v>9.999521347884357</v>
       </c>
       <c r="O212" t="n">
-        <v>0.06918468874269447</v>
+        <v>0.06918468874271679</v>
       </c>
     </row>
     <row r="213">
@@ -11366,7 +11378,7 @@
         <v>1.119868849320314</v>
       </c>
       <c r="O213" t="n">
-        <v>2.622170513731882</v>
+        <v>2.622170513731825</v>
       </c>
     </row>
     <row r="214">
@@ -11388,7 +11400,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -11464,7 +11476,7 @@
         <v>11.47849416044419</v>
       </c>
       <c r="O215" t="n">
-        <v>14.52858681131507</v>
+        <v>14.5285868113164</v>
       </c>
     </row>
     <row r="216">
@@ -11517,7 +11529,7 @@
         <v>41.62693854106835</v>
       </c>
       <c r="O216" t="n">
-        <v>21.72120725956625</v>
+        <v>21.72120725956925</v>
       </c>
     </row>
     <row r="217">
@@ -11570,7 +11582,7 @@
         <v>8.140436530729465</v>
       </c>
       <c r="O217" t="n">
-        <v>3.892037576760444</v>
+        <v>3.89203757676102</v>
       </c>
     </row>
     <row r="218">
@@ -11623,7 +11635,7 @@
         <v>3.110817537813517</v>
       </c>
       <c r="O218" t="n">
-        <v>3.446243392519614</v>
+        <v>3.446243392519586</v>
       </c>
     </row>
     <row r="219">
@@ -11645,7 +11657,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -11721,7 +11733,7 @@
         <v>4.203634884166187</v>
       </c>
       <c r="O220" t="n">
-        <v>4.875392061264012</v>
+        <v>4.875392061263477</v>
       </c>
     </row>
     <row r="221">
@@ -11774,7 +11786,7 @@
         <v>5.387019911928011</v>
       </c>
       <c r="O221" t="n">
-        <v>5.691743311186007</v>
+        <v>5.691743311186354</v>
       </c>
     </row>
     <row r="222">
@@ -11796,7 +11808,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -11872,7 +11884,7 @@
         <v>4.207288914417002</v>
       </c>
       <c r="O223" t="n">
-        <v>4.875310707480775</v>
+        <v>4.875310707480498</v>
       </c>
     </row>
     <row r="224">
@@ -11925,7 +11937,7 @@
         <v>4.893080605016275</v>
       </c>
       <c r="O224" t="n">
-        <v>5.102097546546908</v>
+        <v>5.102097546547108</v>
       </c>
     </row>
     <row r="225">
@@ -11947,7 +11959,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -12023,7 +12035,7 @@
         <v>0.4123133256748994</v>
       </c>
       <c r="O226" t="n">
-        <v>0.9906811184258735</v>
+        <v>0.9906811184260919</v>
       </c>
     </row>
     <row r="227">
@@ -12073,10 +12085,10 @@
         <v>12</v>
       </c>
       <c r="N227" t="n">
-        <v>0.7754628565958261</v>
+        <v>0.7754628565958263</v>
       </c>
       <c r="O227" t="n">
-        <v>1.883625266492334</v>
+        <v>1.883625266493189</v>
       </c>
     </row>
     <row r="228">
@@ -12129,7 +12141,7 @@
         <v>28.90565288148573</v>
       </c>
       <c r="O228" t="n">
-        <v>98.33065886174026</v>
+        <v>98.33065886175632</v>
       </c>
     </row>
     <row r="229">
@@ -12182,7 +12194,7 @@
         <v>27.72684281064522</v>
       </c>
       <c r="O229" t="n">
-        <v>138.6870225122885</v>
+        <v>138.6870225122619</v>
       </c>
     </row>
     <row r="230">
@@ -12235,7 +12247,7 @@
         <v>26.55444189163316</v>
       </c>
       <c r="O230" t="n">
-        <v>155.1598712500914</v>
+        <v>155.1598712500976</v>
       </c>
     </row>
     <row r="231">
@@ -12288,7 +12300,7 @@
         <v>21.02948497032357</v>
       </c>
       <c r="O231" t="n">
-        <v>169.838556199564</v>
+        <v>169.8385561995599</v>
       </c>
     </row>
     <row r="232">
@@ -12341,7 +12353,7 @@
         <v>140.3632107983917</v>
       </c>
       <c r="O232" t="n">
-        <v>172.74230320741</v>
+        <v>172.742303207419</v>
       </c>
     </row>
     <row r="233">
@@ -12394,7 +12406,7 @@
         <v>140.547735975493</v>
       </c>
       <c r="O233" t="n">
-        <v>172.5792594182077</v>
+        <v>172.5792594181736</v>
       </c>
     </row>
     <row r="234">
@@ -12447,7 +12459,7 @@
         <v>953.3480782946582</v>
       </c>
       <c r="O234" t="n">
-        <v>918.5255831966498</v>
+        <v>918.5255831965961</v>
       </c>
     </row>
     <row r="235">
@@ -12497,10 +12509,10 @@
         <v>19.828794</v>
       </c>
       <c r="N235" t="n">
-        <v>6.603293164560597</v>
+        <v>6.603293164560599</v>
       </c>
       <c r="O235" t="n">
-        <v>6.422740308282709</v>
+        <v>6.422740308282895</v>
       </c>
     </row>
     <row r="236">
@@ -12553,7 +12565,7 @@
         <v>5.224594036904078</v>
       </c>
       <c r="O236" t="n">
-        <v>5.118042352604133</v>
+        <v>5.118042352603934</v>
       </c>
     </row>
     <row r="237">
@@ -12606,7 +12618,7 @@
         <v>1.540484144265748</v>
       </c>
       <c r="O237" t="n">
-        <v>1.973378873176647</v>
+        <v>1.973378873176483</v>
       </c>
     </row>
     <row r="238">
@@ -12659,7 +12671,7 @@
         <v>1.209022260817538</v>
       </c>
       <c r="O238" t="n">
-        <v>2.014423653864372</v>
+        <v>2.014423653864279</v>
       </c>
     </row>
     <row r="239">
@@ -12712,7 +12724,7 @@
         <v>9.449085863153361</v>
       </c>
       <c r="O239" t="n">
-        <v>14.66577079265872</v>
+        <v>14.66577079265942</v>
       </c>
     </row>
     <row r="240">
@@ -12765,7 +12777,7 @@
         <v>1567.124028818112</v>
       </c>
       <c r="O240" t="n">
-        <v>1506.044791527829</v>
+        <v>1506.044791527961</v>
       </c>
     </row>
     <row r="241">
@@ -12818,7 +12830,7 @@
         <v>51.19447159999043</v>
       </c>
       <c r="O241" t="n">
-        <v>6.903000670249988</v>
+        <v>6.903000670250046</v>
       </c>
     </row>
     <row r="242">
@@ -12871,7 +12883,7 @@
         <v>22.75287719079073</v>
       </c>
       <c r="O242" t="n">
-        <v>7.990233322796029</v>
+        <v>7.990233322796067</v>
       </c>
     </row>
     <row r="243">
@@ -12924,7 +12936,7 @@
         <v>5.46738123870381</v>
       </c>
       <c r="O243" t="n">
-        <v>2.544680894547987</v>
+        <v>2.544680894547993</v>
       </c>
     </row>
     <row r="244">
@@ -12974,10 +12986,10 @@
         <v>2.08904</v>
       </c>
       <c r="N244" t="n">
-        <v>0.9247152518667432</v>
+        <v>0.9247152518667433</v>
       </c>
       <c r="O244" t="n">
-        <v>0.1542375012537662</v>
+        <v>0.1542375012537665</v>
       </c>
     </row>
     <row r="245">
@@ -13030,7 +13042,7 @@
         <v>1.077312842954241</v>
       </c>
       <c r="O245" t="n">
-        <v>0.1609230617254753</v>
+        <v>0.1609230617254752</v>
       </c>
     </row>
     <row r="246">
@@ -13080,10 +13092,10 @@
         <v>6.093821</v>
       </c>
       <c r="N246" t="n">
-        <v>3.341771317298487</v>
+        <v>3.341771317298488</v>
       </c>
       <c r="O246" t="n">
-        <v>2.398686531752508</v>
+        <v>2.398686531752511</v>
       </c>
     </row>
     <row r="247">
@@ -13136,7 +13148,7 @@
         <v>3.353362729753016</v>
       </c>
       <c r="O247" t="n">
-        <v>2.394066876893433</v>
+        <v>2.394066876893435</v>
       </c>
     </row>
     <row r="248">
@@ -13189,7 +13201,7 @@
         <v>0.5064618035611718</v>
       </c>
       <c r="O248" t="n">
-        <v>0.4999702090842232</v>
+        <v>0.4999702090842933</v>
       </c>
     </row>
     <row r="249">
@@ -13242,7 +13254,7 @@
         <v>0.5063660731380433</v>
       </c>
       <c r="O249" t="n">
-        <v>0.4999714372327366</v>
+        <v>0.4999714372326872</v>
       </c>
     </row>
     <row r="250">
@@ -13295,7 +13307,7 @@
         <v>0.5059831514455294</v>
       </c>
       <c r="O250" t="n">
-        <v>0.4999761664928662</v>
+        <v>0.4999761664928588</v>
       </c>
     </row>
     <row r="251">
@@ -13348,7 +13360,7 @@
         <v>0.5055523645414512</v>
       </c>
       <c r="O251" t="n">
-        <v>0.4999811362921521</v>
+        <v>0.4999811362921581</v>
       </c>
     </row>
     <row r="252">
@@ -13401,7 +13413,7 @@
         <v>0.5367601567333471</v>
       </c>
       <c r="O252" t="n">
-        <v>0.4986597147594298</v>
+        <v>0.4986597147594521</v>
       </c>
     </row>
     <row r="253">
@@ -13454,7 +13466,7 @@
         <v>0.5058395558108367</v>
       </c>
       <c r="O253" t="n">
-        <v>0.4999778643413313</v>
+        <v>0.4999778643414046</v>
       </c>
     </row>
     <row r="254">
@@ -13507,7 +13519,7 @@
         <v>0.5060788818686579</v>
       </c>
       <c r="O254" t="n">
-        <v>0.4999750116776603</v>
+        <v>0.4999750116776375</v>
       </c>
     </row>
     <row r="255">
@@ -13560,7 +13572,7 @@
         <v>0.5058874210224009</v>
       </c>
       <c r="O255" t="n">
-        <v>0.4999773029750679</v>
+        <v>0.4999773029750796</v>
       </c>
     </row>
     <row r="256">
@@ -13613,7 +13625,7 @@
         <v>0.5046429255217308</v>
       </c>
       <c r="O256" t="n">
-        <v>0.4999904089944323</v>
+        <v>0.4999904089943977</v>
       </c>
     </row>
     <row r="257">
@@ -13666,7 +13678,7 @@
         <v>0.5044035994639097</v>
       </c>
       <c r="O257" t="n">
-        <v>0.4999925742040754</v>
+        <v>0.4999925742040336</v>
       </c>
     </row>
     <row r="258">
@@ -13688,7 +13700,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -13761,10 +13773,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="N259" t="n">
-        <v>68.65313038483632</v>
+        <v>68.6531303848363</v>
       </c>
       <c r="O259" t="n">
-        <v>38.268954249866</v>
+        <v>38.26895424986938</v>
       </c>
     </row>
     <row r="260">
@@ -13817,7 +13829,7 @@
         <v>3.744891824621865</v>
       </c>
       <c r="O260" t="n">
-        <v>2.137971774683864</v>
+        <v>2.137971774683935</v>
       </c>
     </row>
     <row r="261">
@@ -13839,7 +13851,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -13915,7 +13927,7 @@
         <v>30.61601569978939</v>
       </c>
       <c r="O262" t="n">
-        <v>16.94740814177757</v>
+        <v>16.94740814177441</v>
       </c>
     </row>
     <row r="263">
@@ -13965,10 +13977,10 @@
         <v>5.77</v>
       </c>
       <c r="N263" t="n">
-        <v>4.244820984108749</v>
+        <v>4.24482098410875</v>
       </c>
       <c r="O263" t="n">
-        <v>2.350774866782062</v>
+        <v>2.350774866782147</v>
       </c>
     </row>
     <row r="264">
@@ -14021,7 +14033,7 @@
         <v>59.20992724487842</v>
       </c>
       <c r="O264" t="n">
-        <v>98.41960113300895</v>
+        <v>98.41960113301627</v>
       </c>
     </row>
     <row r="265">
@@ -14071,10 +14083,10 @@
         <v>61.5</v>
       </c>
       <c r="N265" t="n">
-        <v>59.16812176909821</v>
+        <v>59.16812176909823</v>
       </c>
       <c r="O265" t="n">
-        <v>98.41874590348912</v>
+        <v>98.41874590350844</v>
       </c>
     </row>
     <row r="266">
@@ -14127,7 +14139,7 @@
         <v>59.04909056098028</v>
       </c>
       <c r="O266" t="n">
-        <v>139.1969290066643</v>
+        <v>139.1969290066632</v>
       </c>
     </row>
     <row r="267">
@@ -14180,7 +14192,7 @@
         <v>25.98268236645606</v>
       </c>
       <c r="O267" t="n">
-        <v>138.7317808854285</v>
+        <v>138.7317808854183</v>
       </c>
     </row>
     <row r="268">
@@ -14233,7 +14245,7 @@
         <v>63.8499329887038</v>
       </c>
       <c r="O268" t="n">
-        <v>139.2626129785068</v>
+        <v>139.2626129785178</v>
       </c>
     </row>
     <row r="269">
@@ -14283,10 +14295,10 @@
         <v>45.7</v>
       </c>
       <c r="N269" t="n">
-        <v>43.10179973195482</v>
+        <v>43.10179973195481</v>
       </c>
       <c r="O269" t="n">
-        <v>138.9686255187693</v>
+        <v>138.9686255187514</v>
       </c>
     </row>
     <row r="270">
@@ -14336,10 +14348,10 @@
         <v>56.3</v>
       </c>
       <c r="N270" t="n">
-        <v>40.81888761248325</v>
+        <v>40.81888761248324</v>
       </c>
       <c r="O270" t="n">
-        <v>138.9685751663851</v>
+        <v>138.968575166376</v>
       </c>
     </row>
     <row r="271">
@@ -14392,7 +14404,7 @@
         <v>10.43686578594677</v>
       </c>
       <c r="O271" t="n">
-        <v>138.5175860945418</v>
+        <v>138.5175860945427</v>
       </c>
     </row>
     <row r="272">
@@ -14442,10 +14454,10 @@
         <v>12.4</v>
       </c>
       <c r="N272" t="n">
-        <v>9.984261918437678</v>
+        <v>9.984261918437682</v>
       </c>
       <c r="O272" t="n">
-        <v>138.510320898898</v>
+        <v>138.5103208989194</v>
       </c>
     </row>
     <row r="273">
@@ -14498,7 +14510,7 @@
         <v>43.03801455102431</v>
       </c>
       <c r="O273" t="n">
-        <v>138.9680695396584</v>
+        <v>138.9680695396815</v>
       </c>
     </row>
     <row r="274">
@@ -14551,7 +14563,7 @@
         <v>40.77588550641394</v>
       </c>
       <c r="O274" t="n">
-        <v>170.1810972309433</v>
+        <v>170.181097230918</v>
       </c>
     </row>
     <row r="275">
@@ -14604,7 +14616,7 @@
         <v>40715.46530960521</v>
       </c>
       <c r="O275" t="n">
-        <v>27102.44280217791</v>
+        <v>27102.44280217829</v>
       </c>
     </row>
     <row r="276">
@@ -14710,7 +14722,7 @@
         <v>92143.81013805917</v>
       </c>
       <c r="O277" t="n">
-        <v>83767.66750643424</v>
+        <v>83767.66750643356</v>
       </c>
     </row>
     <row r="278">
@@ -14763,7 +14775,7 @@
         <v>0.7326249282021826</v>
       </c>
       <c r="O278" t="n">
-        <v>7.20882017782238</v>
+        <v>7.208820177822645</v>
       </c>
     </row>
     <row r="279">
@@ -14816,7 +14828,7 @@
         <v>1.704862706490523</v>
       </c>
       <c r="O279" t="n">
-        <v>5.479882962454411</v>
+        <v>5.479882962454016</v>
       </c>
     </row>
     <row r="280">
@@ -14869,7 +14881,7 @@
         <v>0.0880153092092667</v>
       </c>
       <c r="O280" t="n">
-        <v>1.548607763219867</v>
+        <v>1.548607763219739</v>
       </c>
     </row>
     <row r="281">
@@ -14922,7 +14934,7 @@
         <v>26.56044859640054</v>
       </c>
       <c r="O281" t="n">
-        <v>11.04303639641457</v>
+        <v>11.04303639641467</v>
       </c>
     </row>
     <row r="282">
@@ -14972,10 +14984,10 @@
         <v>18.740808</v>
       </c>
       <c r="N282" t="n">
-        <v>7.87527416542217</v>
+        <v>7.875274165422172</v>
       </c>
       <c r="O282" t="n">
-        <v>7.427631338686036</v>
+        <v>7.427631338686292</v>
       </c>
     </row>
     <row r="283">
@@ -15028,7 +15040,7 @@
         <v>16.96207810118706</v>
       </c>
       <c r="O283" t="n">
-        <v>17.77265125512456</v>
+        <v>17.77265125512315</v>
       </c>
     </row>
     <row r="284">
@@ -15081,7 +15093,7 @@
         <v>1.702885578977599</v>
       </c>
       <c r="O284" t="n">
-        <v>1.699577073692295</v>
+        <v>1.699577073692349</v>
       </c>
     </row>
     <row r="285">
@@ -15131,10 +15143,10 @@
         <v>2.250222</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2989835646180356</v>
+        <v>0.2989835646180357</v>
       </c>
       <c r="O285" t="n">
-        <v>0.4501351838839017</v>
+        <v>0.4501351838839213</v>
       </c>
     </row>
     <row r="286">
@@ -15184,10 +15196,10 @@
         <v>1.474398</v>
       </c>
       <c r="N286" t="n">
-        <v>0.9147562254451465</v>
+        <v>0.9147562254451466</v>
       </c>
       <c r="O286" t="n">
-        <v>0.1171262559138805</v>
+        <v>0.1171262559138816</v>
       </c>
     </row>
     <row r="287">
@@ -15399,7 +15411,7 @@
         <v>7.519002165900823</v>
       </c>
       <c r="O290" t="n">
-        <v>0.4113675632296021</v>
+        <v>0.4113675632295899</v>
       </c>
     </row>
     <row r="291">
@@ -15452,7 +15464,7 @@
         <v>8.24776483697109</v>
       </c>
       <c r="O291" t="n">
-        <v>0.3992323710919778</v>
+        <v>0.3992323710919813</v>
       </c>
     </row>
     <row r="292">
@@ -15505,7 +15517,7 @@
         <v>4.895374714148956</v>
       </c>
       <c r="O292" t="n">
-        <v>0.02205165818835634</v>
+        <v>0.02205165818835484</v>
       </c>
     </row>
     <row r="293">
@@ -15555,10 +15567,10 @@
         <v>6.312091</v>
       </c>
       <c r="N293" t="n">
-        <v>5.977998818112197</v>
+        <v>5.977998818112195</v>
       </c>
       <c r="O293" t="n">
-        <v>0.03483331694081224</v>
+        <v>0.03483331694081235</v>
       </c>
     </row>
     <row r="294">
@@ -15611,7 +15623,7 @@
         <v>1.087763251771013</v>
       </c>
       <c r="O294" t="n">
-        <v>0.04335420404484942</v>
+        <v>0.04335420404484969</v>
       </c>
     </row>
     <row r="295">
@@ -15664,7 +15676,7 @@
         <v>0.9196565073743016</v>
       </c>
       <c r="O295" t="n">
-        <v>0.1516511045196784</v>
+        <v>0.1516511045196779</v>
       </c>
     </row>
     <row r="296">
@@ -15686,7 +15698,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>datetime64[us]</t>
+          <t>datetime64[ns]</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -15731,7 +15743,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -15804,10 +15816,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="N298" t="n">
-        <v>68.65313038483632</v>
+        <v>68.6531303848363</v>
       </c>
       <c r="O298" t="n">
-        <v>38.26987020238584</v>
+        <v>38.26987020239017</v>
       </c>
     </row>
     <row r="299">
@@ -15860,7 +15872,7 @@
         <v>3.744891824621865</v>
       </c>
       <c r="O299" t="n">
-        <v>2.138022946205865</v>
+        <v>2.138022946205909</v>
       </c>
     </row>
     <row r="300">
@@ -15882,7 +15894,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>object</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -15958,7 +15970,7 @@
         <v>30.61601569978939</v>
       </c>
       <c r="O301" t="n">
-        <v>16.94781377139292</v>
+        <v>16.94781377138981</v>
       </c>
     </row>
     <row r="302">
@@ -16011,7 +16023,7 @@
         <v>4.24482098410875</v>
       </c>
       <c r="O302" t="n">
-        <v>2.350831131663218</v>
+        <v>2.350831131663233</v>
       </c>
     </row>
     <row r="303">
@@ -16064,7 +16076,7 @@
         <v>59.20992724487842</v>
       </c>
       <c r="O303" t="n">
-        <v>98.42195676784209</v>
+        <v>98.4219567678356</v>
       </c>
     </row>
     <row r="304">
@@ -16114,10 +16126,10 @@
         <v>61.5</v>
       </c>
       <c r="N304" t="n">
-        <v>59.16812176909821</v>
+        <v>59.16812176909823</v>
       </c>
       <c r="O304" t="n">
-        <v>98.42110151785269</v>
+        <v>98.42110151784166</v>
       </c>
     </row>
     <row r="305">
@@ -16170,7 +16182,7 @@
         <v>59.04909056098028</v>
       </c>
       <c r="O305" t="n">
-        <v>139.2002606309633</v>
+        <v>139.2002606309573</v>
       </c>
     </row>
     <row r="306">
@@ -16223,7 +16235,7 @@
         <v>25.98268236645606</v>
       </c>
       <c r="O306" t="n">
-        <v>138.7351013765883</v>
+        <v>138.7351013765672</v>
       </c>
     </row>
     <row r="307">
@@ -16276,7 +16288,7 @@
         <v>63.8499329887038</v>
       </c>
       <c r="O307" t="n">
-        <v>139.2659461749261</v>
+        <v>139.2659461749126</v>
       </c>
     </row>
     <row r="308">
@@ -16326,10 +16338,10 @@
         <v>45.7</v>
       </c>
       <c r="N308" t="n">
-        <v>43.10179973195482</v>
+        <v>43.10179973195481</v>
       </c>
       <c r="O308" t="n">
-        <v>138.9719516787133</v>
+        <v>138.9719516787141</v>
       </c>
     </row>
     <row r="309">
@@ -16382,7 +16394,7 @@
         <v>40.81888761248324</v>
       </c>
       <c r="O309" t="n">
-        <v>138.9719013251239</v>
+        <v>138.971901325124</v>
       </c>
     </row>
     <row r="310">
@@ -16435,7 +16447,7 @@
         <v>10.43686578594677</v>
       </c>
       <c r="O310" t="n">
-        <v>138.5209014590327</v>
+        <v>138.520901459037</v>
       </c>
     </row>
     <row r="311">
@@ -16485,10 +16497,10 @@
         <v>12.4</v>
       </c>
       <c r="N311" t="n">
-        <v>9.98426191843768</v>
+        <v>9.984261918437682</v>
       </c>
       <c r="O311" t="n">
-        <v>138.5136360894994</v>
+        <v>138.513636089517</v>
       </c>
     </row>
     <row r="312">
@@ -16541,7 +16553,7 @@
         <v>43.03801455102431</v>
       </c>
       <c r="O312" t="n">
-        <v>138.9713956862952</v>
+        <v>138.9713956862927</v>
       </c>
     </row>
     <row r="313">
@@ -16594,7 +16606,7 @@
         <v>40.77588550641394</v>
       </c>
       <c r="O313" t="n">
-        <v>170.1851704492451</v>
+        <v>170.1851704492484</v>
       </c>
     </row>
     <row r="314">
@@ -16750,10 +16762,10 @@
         <v>253827.408</v>
       </c>
       <c r="N316" t="n">
-        <v>92143.81013805915</v>
+        <v>92143.81013805917</v>
       </c>
       <c r="O316" t="n">
-        <v>83769.67245294082</v>
+        <v>83769.67245294117</v>
       </c>
     </row>
     <row r="317">
@@ -16806,7 +16818,7 @@
         <v>0.7326249282021826</v>
       </c>
       <c r="O317" t="n">
-        <v>7.208992718126561</v>
+        <v>7.208992718126024</v>
       </c>
     </row>
     <row r="318">
@@ -16859,7 +16871,7 @@
         <v>1.704862706490523</v>
       </c>
       <c r="O318" t="n">
-        <v>5.480014121319509</v>
+        <v>5.480014121319283</v>
       </c>
     </row>
     <row r="319">
@@ -16912,7 +16924,7 @@
         <v>0.0880153092092667</v>
       </c>
       <c r="O319" t="n">
-        <v>1.548644828543725</v>
+        <v>1.548644828543889</v>
       </c>
     </row>
     <row r="320">
@@ -16965,7 +16977,7 @@
         <v>26.56044859640054</v>
       </c>
       <c r="O320" t="n">
-        <v>11.04330070719108</v>
+        <v>11.04330070719121</v>
       </c>
     </row>
     <row r="321">
@@ -17015,10 +17027,10 @@
         <v>18.740808</v>
       </c>
       <c r="N321" t="n">
-        <v>7.87527416542217</v>
+        <v>7.875274165422172</v>
       </c>
       <c r="O321" t="n">
-        <v>7.427809116150158</v>
+        <v>7.427809116150036</v>
       </c>
     </row>
     <row r="322">
@@ -17071,7 +17083,7 @@
         <v>16.96207810118706</v>
       </c>
       <c r="O322" t="n">
-        <v>17.77307663661252</v>
+        <v>17.77307663661151</v>
       </c>
     </row>
     <row r="323">
@@ -17124,7 +17136,7 @@
         <v>1.702885578977599</v>
       </c>
       <c r="O323" t="n">
-        <v>1.699617752407818</v>
+        <v>1.699617752407825</v>
       </c>
     </row>
     <row r="324">
@@ -17174,10 +17186,10 @@
         <v>2.250222</v>
       </c>
       <c r="N324" t="n">
-        <v>0.2989835646180355</v>
+        <v>0.2989835646180357</v>
       </c>
       <c r="O324" t="n">
-        <v>0.4501459576942666</v>
+        <v>0.4501459576942841</v>
       </c>
     </row>
     <row r="325">
@@ -17227,10 +17239,10 @@
         <v>1.474398</v>
       </c>
       <c r="N325" t="n">
-        <v>0.9147562254451465</v>
+        <v>0.9147562254451466</v>
       </c>
       <c r="O325" t="n">
-        <v>0.1171290592852123</v>
+        <v>0.1171290592852135</v>
       </c>
     </row>
     <row r="326">
@@ -17442,7 +17454,7 @@
         <v>7.519002165900823</v>
       </c>
       <c r="O329" t="n">
-        <v>0.4113774091520608</v>
+        <v>0.4113774091520602</v>
       </c>
     </row>
     <row r="330">
@@ -17495,7 +17507,7 @@
         <v>8.24776483697109</v>
       </c>
       <c r="O330" t="n">
-        <v>0.3992419265633376</v>
+        <v>0.3992419265633381</v>
       </c>
     </row>
     <row r="331">
@@ -17545,10 +17557,10 @@
         <v>5.138357</v>
       </c>
       <c r="N331" t="n">
-        <v>4.895374714148956</v>
+        <v>4.895374714148957</v>
       </c>
       <c r="O331" t="n">
-        <v>0.0220521859862092</v>
+        <v>0.02205218598621059</v>
       </c>
     </row>
     <row r="332">
@@ -17601,7 +17613,7 @@
         <v>5.977998818112196</v>
       </c>
       <c r="O332" t="n">
-        <v>0.03483415066269077</v>
+        <v>0.03483415066269094</v>
       </c>
     </row>
     <row r="333">
@@ -17654,7 +17666,7 @@
         <v>1.087763251771013</v>
       </c>
       <c r="O333" t="n">
-        <v>0.04335524171084315</v>
+        <v>0.04335524171084323</v>
       </c>
     </row>
     <row r="334">
@@ -17707,7 +17719,7 @@
         <v>0.9196565073743016</v>
       </c>
       <c r="O334" t="n">
-        <v>0.1516553409982322</v>
+        <v>0.1516553409982321</v>
       </c>
     </row>
   </sheetData>
